--- a/XLibur.Tests/Resource/Other/Formulas/DataTableFormula-Output.xlsx
+++ b/XLibur.Tests/Resource/Other/Formulas/DataTableFormula-Output.xlsx
@@ -48,9 +48,6 @@
     <x:t>Row Data Formula</x:t>
   </x:si>
   <x:si>
-    <x:t>Z</x:t>
-  </x:si>
-  <x:si>
     <x:t>Column Data Formula</x:t>
   </x:si>
   <x:si>
@@ -67,6 +64,9 @@
   </x:si>
   <x:si>
     <x:t>E</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Z</x:t>
   </x:si>
   <x:si>
     <x:t>2D 1x1</x:t>
@@ -531,29 +531,29 @@
   <x:sheetData>
     <x:row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <x:c r="A1" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <x:c r="B2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <x:c r="C3" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="E3" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="F3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
+      <x:c r="G3" s="0" t="s">
         <x:v>6</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -611,7 +611,7 @@
     </x:row>
     <x:row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <x:c r="B5" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C5" s="0" t="str">
         <x:f t="dataTable" ref="C5" dt2D="1" r1="B8" r2="B7" ca="1"/>
@@ -623,7 +623,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -656,7 +656,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -681,7 +681,7 @@
     </x:row>
     <x:row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <x:c r="B5" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C5" s="0" t="str">
         <x:f t="dataTable" ref="C5:D8" dt2D="1" r1="B2" r2="B1" ca="1"/>
@@ -693,7 +693,7 @@
     </x:row>
     <x:row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <x:c r="B6" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="0" t="str">
         <x:v>B2</x:v>
@@ -704,7 +704,7 @@
     </x:row>
     <x:row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <x:c r="B7" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C7" s="0" t="str">
         <x:v>C2</x:v>
@@ -715,7 +715,7 @@
     </x:row>
     <x:row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <x:c r="B8" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="0" t="str">
         <x:v>D2</x:v>
@@ -791,24 +791,24 @@
   <x:sheetData>
     <x:row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <x:c r="A2" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <x:c r="B3" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="D3" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="E3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="F3" s="0" t="s">
         <x:v>6</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -852,7 +852,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <x:c r="A1" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -869,7 +869,7 @@
     </x:row>
     <x:row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <x:c r="C4" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D4" s="0" t="e">
         <x:f t="dataTable" ref="D4:E6" dt2D="1" r1="A2" del1="1" r2="A1" ca="1"/>
@@ -881,7 +881,7 @@
     </x:row>
     <x:row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <x:c r="C5" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D5" s="0" t="e">
         <x:v>#REF!</x:v>
@@ -892,7 +892,7 @@
     </x:row>
     <x:row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <x:c r="C6" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D6" s="0" t="e">
         <x:v>#REF!</x:v>
@@ -937,7 +937,7 @@
     </x:row>
     <x:row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <x:c r="B3" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="0" t="e">
         <x:f t="dataTable" ref="C3:D5" dt2D="1" r1="A1" r2="A1" del2="1" ca="1"/>
@@ -949,7 +949,7 @@
     </x:row>
     <x:row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="0" t="e">
         <x:v>#REF!</x:v>
@@ -960,7 +960,7 @@
     </x:row>
     <x:row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <x:c r="B5" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="0" t="e">
         <x:v>#REF!</x:v>
@@ -1000,7 +1000,7 @@
     </x:row>
     <x:row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <x:c r="B2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="0" t="e">
         <x:f t="dataTable" ref="C2:D4" dt2D="1" r1="A2" del1="1" r2="A1" del2="1" ca="1"/>
@@ -1012,7 +1012,7 @@
     </x:row>
     <x:row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C3" s="0" t="e">
         <x:v>#REF!</x:v>
@@ -1023,7 +1023,7 @@
     </x:row>
     <x:row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <x:c r="B4" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C4" s="0" t="e">
         <x:v>#REF!</x:v>

--- a/XLibur.Tests/Resource/Other/Formulas/DataTableFormula-Output.xlsx
+++ b/XLibur.Tests/Resource/Other/Formulas/DataTableFormula-Output.xlsx
@@ -449,14 +449,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{7E63D0D3-E684-4318-BD37-D980BEE3415E}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C8"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:sheetData>
     <x:row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="A1" s="0">
+      <x:c r="A1">
         <x:v>0.5</x:v>
       </x:c>
     </x:row>
@@ -466,71 +463,65 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="C3" s="0">
+      <x:c r="C3">
         <x:f>A1*10</x:f>
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="B4" s="0">
+      <x:c r="B4">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C4" s="0">
+      <x:c r="C4">
         <x:f t="dataTable" ref="C4:C8" r1="A1" ca="1"/>
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="B5" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
+      <x:c r="B5">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="B6" s="0">
+      <x:c r="B6">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C6" s="0">
+      <x:c r="C6">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="B7" s="0">
+      <x:c r="B7">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C7" s="0">
+      <x:c r="C7">
         <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="B8" s="0">
+      <x:c r="B8">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C8" s="0">
+      <x:c r="C8">
         <x:v>50</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" r:id="rId1"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageSetup orientation="portrait" r:id="rId1"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{7815406A-D0FC-49B5-9D93-10E1A22A83C2}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:G4"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:sheetData>
     <x:row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -540,58 +531,51 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <x:c r="C3" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="C3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="E3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
+      <x:c r="F3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="G3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <x:c r="B4" s="0" t="str">
+      <x:c r="B4" t="str">
         <x:f>REPT(A1,2)</x:f>
         <x:v>ZZ</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="str">
+      <x:c r="C4" t="str">
         <x:f t="dataTable" ref="C4:G4" dtr="1" r1="A1" ca="1"/>
         <x:v>AA</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="str">
+      <x:c r="D4" t="str">
         <x:v>BB</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="str">
+      <x:c r="E4" t="str">
         <x:v>CC</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="str">
+      <x:c r="F4" t="str">
         <x:v>DD</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="str">
+      <x:c r="G4" t="str">
         <x:v>EE</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{DB2218BA-CDA8-4620-A6D5-67347E235271}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A2:C8"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:sheetData>
@@ -601,69 +585,62 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="B4" s="0" t="str">
+      <x:c r="B4" t="str">
         <x:f>B7 &amp; B8</x:f>
         <x:v>A1</x:v>
       </x:c>
-      <x:c r="C4" s="0">
+      <x:c r="C4">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="str">
+      <x:c r="C5" t="str">
         <x:f t="dataTable" ref="C5" dt2D="1" r1="B8" r2="B7" ca="1"/>
         <x:v>Z10</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="A7" s="0" t="s">
+      <x:c r="A7" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="B7" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="A8" s="0" t="s">
+      <x:c r="A8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B8" s="0">
+      <x:c r="B8">
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{754CF9A6-AF52-42D5-A3E0-DC7A1C8B8C6B}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:D8"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:sheetData>
     <x:row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B2" s="0">
+      <x:c r="B2">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -672,371 +649,332 @@
         <x:f>B1 &amp; B2</x:f>
         <x:v>Z1</x:v>
       </x:c>
-      <x:c r="C4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="0">
+      <x:c r="C4">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D4">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="B5" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="str">
+      <x:c r="B5" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
         <x:f t="dataTable" ref="C5:D8" dt2D="1" r1="B2" r2="B1" ca="1"/>
         <x:v>A2</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="str">
+      <x:c r="D5" t="str">
         <x:v>A3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="B6" s="0" t="s">
+      <x:c r="B6" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="str">
+      <x:c r="C6" t="str">
         <x:v>B2</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="str">
+      <x:c r="D6" t="str">
         <x:v>B3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="B7" s="0" t="s">
+      <x:c r="B7" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="str">
+      <x:c r="C7" t="str">
         <x:v>C2</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="str">
+      <x:c r="D7" t="str">
         <x:v>C3</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="B8" s="0" t="s">
+      <x:c r="B8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="str">
+      <x:c r="C8" t="str">
         <x:v>D2</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="str">
+      <x:c r="D8" t="str">
         <x:v>D3</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{18FEE19D-7897-4018-81BA-1928189FE47E}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="B2:C5"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:sheetData>
     <x:row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="C2" s="0" t="e">
+      <x:c r="C2" t="e">
         <x:f>#REF!*3</x:f>
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="B3" s="0">
+      <x:c r="B3">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="e">
+      <x:c r="C3" t="e">
         <x:f t="dataTable" ref="C3:C5" dtr="1" r1="B1" del1="1" ca="1"/>
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="B4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="e">
+      <x:c r="B4">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C4" t="e">
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="B5" s="0">
+      <x:c r="B5">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="e">
+      <x:c r="C5" t="e">
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{44D6BFE5-F493-42D0-9BF6-56C8D10A1639}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A2:F4"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:sheetData>
     <x:row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="B3" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="B3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="D3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="E3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
+      <x:c r="F3" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <x:c r="A4" s="0" t="e">
+      <x:c r="A4" t="e">
         <x:f>REPT(#REF!,2)</x:f>
         <x:v>#REF!</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="e">
+      <x:c r="B4" t="e">
         <x:f t="dataTable" ref="B4:F4" dtr="1" r1="A1" del1="1" ca="1"/>
         <x:v>#REF!</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="e">
-        <x:v>#REF!</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="e">
-        <x:v>#REF!</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="e">
-        <x:v>#REF!</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="e">
+      <x:c r="C4" t="e">
+        <x:v>#REF!</x:v>
+      </x:c>
+      <x:c r="D4" t="e">
+        <x:v>#REF!</x:v>
+      </x:c>
+      <x:c r="E4" t="e">
+        <x:v>#REF!</x:v>
+      </x:c>
+      <x:c r="F4" t="e">
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{8DCFBCE9-324E-4CC9-8B02-00C9F0DEF40F}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:E6"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:sheetData>
     <x:row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="C3" s="0" t="e">
+      <x:c r="C3" t="e">
         <x:f>A1&amp;#REF!</x:f>
         <x:v>#REF!</x:v>
       </x:c>
-      <x:c r="D3" s="0">
+      <x:c r="D3">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E3" s="0">
+      <x:c r="E3">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="C4" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="e">
+      <x:c r="C4" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D4" t="e">
         <x:f t="dataTable" ref="D4:E6" dt2D="1" r1="A2" del1="1" r2="A1" ca="1"/>
         <x:v>#REF!</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="e">
+      <x:c r="E4" t="e">
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="C5" s="0" t="s">
+      <x:c r="C5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="e">
-        <x:v>#REF!</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="e">
+      <x:c r="D5" t="e">
+        <x:v>#REF!</x:v>
+      </x:c>
+      <x:c r="E5" t="e">
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <x:c r="C6" s="0" t="s">
+      <x:c r="C6" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="e">
-        <x:v>#REF!</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="e">
+      <x:c r="D6" t="e">
+        <x:v>#REF!</x:v>
+      </x:c>
+      <x:c r="E6" t="e">
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{942B762A-A2AA-4001-82C8-C09F808D552B}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:D5"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:sheetData>
     <x:row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="A1" s="0">
+      <x:c r="A1">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="B2" s="0" t="e">
+      <x:c r="B2" t="e">
         <x:f>#REF!&amp;A1</x:f>
         <x:v>#REF!</x:v>
       </x:c>
-      <x:c r="C2" s="0">
+      <x:c r="C2">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D2" s="0">
+      <x:c r="D2">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="B3" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="e">
+      <x:c r="B3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" t="e">
         <x:f t="dataTable" ref="C3:D5" dt2D="1" r1="A1" r2="A1" del2="1" ca="1"/>
         <x:v>#REF!</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="e">
+      <x:c r="D3" t="e">
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="e">
-        <x:v>#REF!</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="e">
+      <x:c r="C4" t="e">
+        <x:v>#REF!</x:v>
+      </x:c>
+      <x:c r="D4" t="e">
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="e">
-        <x:v>#REF!</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="e">
+      <x:c r="C5" t="e">
+        <x:v>#REF!</x:v>
+      </x:c>
+      <x:c r="D5" t="e">
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{8AA252A3-EED1-4A04-B723-0E1AE3D4B33F}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="B1:D4"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:sheetData>
     <x:row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="B1" s="0" t="e">
+      <x:c r="B1" t="e">
         <x:f>#REF!&amp;#REF!</x:f>
         <x:v>#REF!</x:v>
       </x:c>
-      <x:c r="C1" s="0">
+      <x:c r="C1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D1" s="0">
+      <x:c r="D1">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="B2" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="e">
+      <x:c r="B2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C2" t="e">
         <x:f t="dataTable" ref="C2:D4" dt2D="1" r1="A2" del1="1" r2="A1" del2="1" ca="1"/>
         <x:v>#REF!</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="e">
+      <x:c r="D2" t="e">
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="e">
-        <x:v>#REF!</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="e">
+      <x:c r="C3" t="e">
+        <x:v>#REF!</x:v>
+      </x:c>
+      <x:c r="D3" t="e">
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="e">
-        <x:v>#REF!</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="e">
+      <x:c r="C4" t="e">
+        <x:v>#REF!</x:v>
+      </x:c>
+      <x:c r="D4" t="e">
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>